--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(4).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(4).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20685" windowHeight="11400"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_终局（终） (1)" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="481">
   <si>
     <t>ID</t>
   </si>
@@ -96,6 +96,9 @@
     <t>面对摆在眼前的两个按钮，你的最终决定是？</t>
   </si>
   <si>
+    <t>stop</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=1</t>
   </si>
   <si>
@@ -138,7 +141,7 @@
     <t>亚波伦的身体猛地一弓，喉间滚出一声压抑的闷哼，巨大的能量波动席卷了他的身体，顺着整间手术室的墙壁扩散开来，惨白的灯光开始疯狂闪烁，每一次明暗交替都带着电流滋啦的炸响。</t>
   </si>
   <si>
-    <t>playsfx(ElectricShock)&amp;bgfade(sntzm_final(3)_57,1)</t>
+    <t>parallel(playsfx(ElectricShock);bgfade(sntzm_final(3)_57,1))</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=6</t>
@@ -552,6 +555,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>charfadeout(L,1)&amp;loadScript(</t>
     </r>
     <r>
@@ -1004,6 +1012,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -1028,6 +1041,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -2918,7 +2936,7 @@
         <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J3" t="s">
         <v>15</v>
@@ -2927,12 +2945,12 @@
         <v>15</v>
       </c>
       <c r="L3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" ht="30" spans="1:12">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -2962,15 +2980,15 @@
         <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -3003,12 +3021,12 @@
         <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -3026,7 +3044,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -3041,12 +3059,12 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" ht="55.5" spans="1:12">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -3064,7 +3082,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -3079,12 +3097,12 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="54" spans="1:12">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -3102,7 +3120,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -3114,15 +3132,15 @@
         <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" ht="54" spans="1:12">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -3140,7 +3158,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -3155,15 +3173,15 @@
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
@@ -3178,7 +3196,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -3193,12 +3211,12 @@
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" ht="40.5" spans="1:12">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -3216,7 +3234,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -3231,12 +3249,12 @@
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" ht="42" spans="1:12">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -3254,7 +3272,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3269,12 +3287,12 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" ht="42" spans="1:12">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -3292,7 +3310,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3307,12 +3325,12 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" ht="55.5" spans="1:12">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -3330,7 +3348,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3342,15 +3360,15 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" ht="40.5" spans="1:12">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3368,7 +3386,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3383,15 +3401,15 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
@@ -3406,7 +3424,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3421,12 +3439,12 @@
         <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" ht="27" spans="1:12">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3444,7 +3462,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3459,15 +3477,15 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
@@ -3482,7 +3500,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3497,12 +3515,12 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" ht="27" spans="1:12">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3520,7 +3538,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3535,12 +3553,12 @@
         <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" ht="40.5" spans="1:12">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3558,7 +3576,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3573,15 +3591,15 @@
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" ht="28.5" spans="1:12">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
@@ -3596,7 +3614,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3611,15 +3629,15 @@
         <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" ht="27" spans="1:12">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
@@ -3634,7 +3652,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3649,12 +3667,12 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" ht="42" spans="1:12">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3672,7 +3690,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3687,15 +3705,15 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
@@ -3710,7 +3728,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3725,12 +3743,12 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" ht="54" spans="1:12">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3748,7 +3766,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3763,15 +3781,15 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" ht="27" spans="1:12">
       <c r="A26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
@@ -3786,7 +3804,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3801,12 +3819,12 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" ht="40.5" spans="1:12">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3824,7 +3842,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3836,18 +3854,18 @@
         <v>15</v>
       </c>
       <c r="K27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
@@ -3862,7 +3880,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3877,15 +3895,15 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" ht="27" spans="1:12">
       <c r="A29" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
@@ -3900,7 +3918,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3915,15 +3933,15 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
@@ -3938,7 +3956,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3953,12 +3971,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3991,12 +4009,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" ht="150" spans="1:12">
       <c r="A32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -4014,7 +4032,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -4029,15 +4047,15 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
@@ -4052,7 +4070,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -4064,15 +4082,15 @@
         <v>15</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" ht="150" spans="1:12">
       <c r="A34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -4090,7 +4108,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -4105,12 +4123,12 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" ht="69" spans="1:12">
       <c r="A35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -4128,7 +4146,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -4143,21 +4161,21 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4166,7 +4184,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4178,15 +4196,15 @@
         <v>15</v>
       </c>
       <c r="K36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L36" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" ht="40.5" spans="1:12">
       <c r="A37" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -4195,7 +4213,7 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4204,7 +4222,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4216,15 +4234,15 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L37" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" ht="27" spans="1:12">
       <c r="A38" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4242,7 +4260,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4257,12 +4275,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" ht="55.5" spans="1:12">
       <c r="A39" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4280,7 +4298,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4295,21 +4313,21 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C40" t="s">
         <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4318,7 +4336,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4330,15 +4348,15 @@
         <v>15</v>
       </c>
       <c r="K40" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" ht="30" spans="1:12">
       <c r="A41" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4347,7 +4365,7 @@
         <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4356,7 +4374,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4368,18 +4386,18 @@
         <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L41" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B42" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C42" t="s">
         <v>14</v>
@@ -4394,7 +4412,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4409,12 +4427,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" ht="54" spans="1:12">
       <c r="A43" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4432,7 +4450,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4447,21 +4465,21 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B44" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4470,7 +4488,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4482,15 +4500,15 @@
         <v>15</v>
       </c>
       <c r="K44" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L44" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="45" ht="27" spans="1:12">
       <c r="A45" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4499,7 +4517,7 @@
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -4508,7 +4526,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4523,21 +4541,21 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46" ht="40.5" spans="1:12">
       <c r="A46" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B46" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -4546,7 +4564,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4561,21 +4579,21 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" ht="40.5" spans="1:12">
       <c r="A47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B47" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -4584,7 +4602,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4596,15 +4614,15 @@
         <v>15</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4635,12 +4653,12 @@
       </c>
       <c r="K48"/>
       <c r="L48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" ht="28.5" spans="1:12">
       <c r="A49" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4658,7 +4676,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4673,12 +4691,12 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50" ht="54" spans="1:12">
       <c r="A50" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4696,7 +4714,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4711,12 +4729,12 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" ht="43.5" spans="1:12">
       <c r="A51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4734,7 +4752,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4749,12 +4767,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52" ht="69" spans="1:12">
       <c r="A52" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4772,7 +4790,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4787,12 +4805,12 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53" ht="27" spans="1:12">
       <c r="A53" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4810,7 +4828,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4825,12 +4843,12 @@
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="54" ht="27" spans="1:12">
       <c r="A54" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4848,7 +4866,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4863,12 +4881,12 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55" ht="40.5" spans="1:12">
       <c r="A55" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4886,7 +4904,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4898,15 +4916,15 @@
         <v>15</v>
       </c>
       <c r="K55" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L55" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" ht="55.5" spans="1:12">
       <c r="A56" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4924,7 +4942,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4939,15 +4957,15 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B57" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
@@ -4962,7 +4980,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4977,12 +4995,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="58" ht="40.5" spans="1:12">
       <c r="A58" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -5000,7 +5018,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -5015,12 +5033,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" ht="28.5" spans="1:12">
       <c r="A59" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -5038,7 +5056,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -5053,15 +5071,15 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="60" ht="28.5" spans="1:12">
       <c r="A60" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B60" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
@@ -5076,7 +5094,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5091,12 +5109,12 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="61" ht="54" spans="1:12">
       <c r="A61" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -5114,7 +5132,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5129,12 +5147,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="62" ht="27" spans="1:12">
       <c r="A62" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -5152,7 +5170,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5167,12 +5185,12 @@
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="63" ht="30" spans="1:12">
       <c r="A63" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5190,7 +5208,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5205,12 +5223,12 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="64" ht="55.5" spans="1:12">
       <c r="A64" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5228,7 +5246,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5240,18 +5258,18 @@
         <v>15</v>
       </c>
       <c r="K64" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L64" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B65" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
@@ -5266,7 +5284,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5281,12 +5299,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66" ht="27" spans="1:12">
       <c r="A66" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5304,7 +5322,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5319,12 +5337,12 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="67" ht="42" spans="1:12">
       <c r="A67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5342,7 +5360,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5357,12 +5375,12 @@
         <v>15</v>
       </c>
       <c r="L67" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="68" ht="42" spans="1:12">
       <c r="A68" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5380,7 +5398,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5395,12 +5413,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="69" ht="40.5" spans="1:12">
       <c r="A69" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5418,7 +5436,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5433,12 +5451,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="70" ht="40.5" spans="1:12">
       <c r="A70" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5456,7 +5474,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5471,12 +5489,12 @@
         <v>15</v>
       </c>
       <c r="L70" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5509,12 +5527,12 @@
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="72" ht="150" spans="1:12">
       <c r="A72" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5532,7 +5550,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5544,18 +5562,18 @@
         <v>15</v>
       </c>
       <c r="K72" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L72" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B73" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C73" t="s">
         <v>14</v>
@@ -5570,7 +5588,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5585,12 +5603,12 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="74" ht="27" spans="1:12">
       <c r="A74" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5608,7 +5626,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5623,15 +5641,15 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B75" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C75" t="s">
         <v>14</v>
@@ -5646,7 +5664,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5661,15 +5679,15 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="76" ht="28.5" spans="1:12">
       <c r="A76" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B76" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -5684,7 +5702,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5699,12 +5717,12 @@
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="77" ht="54" spans="1:12">
       <c r="A77" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5722,7 +5740,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5737,15 +5755,15 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B78" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
@@ -5760,7 +5778,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5775,12 +5793,12 @@
         <v>15</v>
       </c>
       <c r="L78" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="79" ht="27" spans="1:12">
       <c r="A79" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5798,7 +5816,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5813,12 +5831,12 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="80" ht="28.5" spans="1:12">
       <c r="A80" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5836,7 +5854,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5851,15 +5869,15 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="81" ht="27" spans="1:12">
       <c r="A81" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B81" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C81" t="s">
         <v>14</v>
@@ -5874,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5889,15 +5907,15 @@
         <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B82" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C82" t="s">
         <v>14</v>
@@ -5912,7 +5930,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5927,12 +5945,12 @@
         <v>15</v>
       </c>
       <c r="L82" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="83" ht="42" spans="1:12">
       <c r="A83" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -5950,7 +5968,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5965,15 +5983,15 @@
         <v>15</v>
       </c>
       <c r="L83" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="84" ht="40.5" spans="1:12">
       <c r="A84" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B84" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C84" t="s">
         <v>14</v>
@@ -5988,7 +6006,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -6003,15 +6021,15 @@
         <v>15</v>
       </c>
       <c r="L84" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="85" ht="27" spans="1:12">
       <c r="A85" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B85" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C85" t="s">
         <v>14</v>
@@ -6026,7 +6044,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6041,12 +6059,12 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="86" ht="54" spans="1:12">
       <c r="A86" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6064,7 +6082,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6079,15 +6097,15 @@
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="87" ht="27" spans="1:12">
       <c r="A87" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B87" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
@@ -6102,7 +6120,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6117,15 +6135,15 @@
         <v>15</v>
       </c>
       <c r="L87" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="88" ht="43.5" spans="1:12">
       <c r="A88" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B88" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
@@ -6140,7 +6158,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6155,12 +6173,12 @@
         <v>15</v>
       </c>
       <c r="L88" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="89" ht="27" spans="1:12">
       <c r="A89" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6178,7 +6196,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6190,15 +6208,15 @@
         <v>15</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L89" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="90" ht="27" spans="1:12">
       <c r="A90" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -6216,7 +6234,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6231,12 +6249,12 @@
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="91" ht="54" spans="1:12">
       <c r="A91" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6254,7 +6272,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6266,18 +6284,18 @@
         <v>15</v>
       </c>
       <c r="K91" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L91" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B92" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C92" t="s">
         <v>14</v>
@@ -6292,7 +6310,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6307,12 +6325,12 @@
         <v>15</v>
       </c>
       <c r="L92" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="93" ht="40.5" spans="1:12">
       <c r="A93" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6330,7 +6348,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6345,12 +6363,12 @@
         <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="94" ht="69" spans="1:12">
       <c r="A94" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -6368,7 +6386,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6383,12 +6401,12 @@
         <v>15</v>
       </c>
       <c r="L94" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="95" ht="42" spans="1:12">
       <c r="A95" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6406,7 +6424,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6418,15 +6436,15 @@
         <v>15</v>
       </c>
       <c r="K95" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L95" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -6450,7 +6468,7 @@
         <v>15</v>
       </c>
       <c r="I96" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J96" t="s">
         <v>15</v>
@@ -6459,12 +6477,12 @@
         <v>15</v>
       </c>
       <c r="L96" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97" ht="30" spans="1:12">
       <c r="A97" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -6494,15 +6512,15 @@
         <v>15</v>
       </c>
       <c r="K97" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L97" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -6532,15 +6550,15 @@
         <v>15</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L98" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -6570,10 +6588,10 @@
         <v>15</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L99" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -6594,39 +6612,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
@@ -6634,82 +6652,82 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B12" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -6731,616 +6749,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E8" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D9" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F10" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C12" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D12" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E12" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F12" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B13" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C13" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D13" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E13" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F13" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B15" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C15" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D15" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E15" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F15" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B16" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C16" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D16" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E16" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F16" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B17" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C17" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D17" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E17" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F17" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B18" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C18" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D18" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E18" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F18" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B19" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C19" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D19" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E19" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F19" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B20" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C20" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D20" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E20" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F20" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B21" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C21" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D21" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E21" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F21" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B22" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C22" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D22" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E22" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F22" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B23" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C23" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D23" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E23" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F23" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B24" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C24" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D24" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E24" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F24" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B25" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C25" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D25" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E25" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F25" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C26" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D26" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E26" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F26" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B27" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C27" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D27" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E27" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F27" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B28" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C28" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D28" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E28" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F28" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B29" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C29" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D29" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E29" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F29" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B30" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C30" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D30" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E30" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F30" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B31" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C31" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D31" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(4).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(4).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20685" windowHeight="11400"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_终局（终） (1)" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="488">
   <si>
     <t>ID</t>
   </si>
@@ -121,6 +121,12 @@
   </si>
   <si>
     <t xml:space="preserve">你的指尖落在右侧的按钮上，不带一丝犹豫。 </t>
+  </si>
+  <si>
+    <t>17 enhanced_suspense-tense-background-music</t>
+  </si>
+  <si>
+    <t>unlockmusic(Music17)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=4</t>
@@ -592,6 +598,9 @@
     <t>你的指尖在左侧按钮的上方悬停了半秒——然后，在大卫来得及阻止你之前，迅速落了下去。</t>
   </si>
   <si>
+    <t>4 enhanced leberch-spooky-piano</t>
+  </si>
+  <si>
     <t>56</t>
   </si>
   <si>
@@ -749,6 +758,12 @@
   </si>
   <si>
     <t>77</t>
+  </si>
+  <si>
+    <t>10 enhanced suspense</t>
+  </si>
+  <si>
+    <t>unlockmusic(Music10)</t>
   </si>
   <si>
     <t>源类型=type:exeBC; 层级=26</t>
@@ -1005,7 +1020,46 @@
     <t>52</t>
   </si>
   <si>
-    <t>choice(选择大卫|jump(53))&amp;choice(选择亚波伦|jump(54))</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>choice(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>选择大卫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>|jump(53))&amp;choice(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>选择亚波伦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>|jump(54))</t>
+    </r>
   </si>
   <si>
     <t>53</t>
@@ -1037,6 +1091,48 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_pb; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=3;tag=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>选择大卫</t>
+    </r>
+  </si>
+  <si>
     <t>54</t>
   </si>
   <si>
@@ -1066,6 +1162,48 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_pb; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=3;tag=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>选择亚波伦</t>
+    </r>
+  </si>
+  <si>
     <t>项目</t>
   </si>
   <si>
@@ -1640,6 +1778,11 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1792,11 +1935,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -2105,31 +2243,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2138,119 +2273,122 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2259,6 +2397,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3024,7 +3165,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" ht="60" spans="1:12">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -3050,21 +3191,21 @@
         <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="J6" t="s">
         <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="L6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" ht="55.5" spans="1:12">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -3082,7 +3223,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -3097,12 +3238,12 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" ht="54" spans="1:12">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -3120,7 +3261,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -3132,15 +3273,15 @@
         <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" ht="54" spans="1:12">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -3158,7 +3299,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -3173,15 +3314,15 @@
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
@@ -3196,7 +3337,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -3211,12 +3352,12 @@
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" ht="40.5" spans="1:12">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -3234,7 +3375,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -3249,12 +3390,12 @@
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" ht="42" spans="1:12">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -3272,7 +3413,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3287,12 +3428,12 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" ht="42" spans="1:12">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -3310,7 +3451,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3325,12 +3466,12 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" ht="55.5" spans="1:12">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -3348,7 +3489,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3360,15 +3501,15 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" ht="40.5" spans="1:12">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3386,7 +3527,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3401,15 +3542,15 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
@@ -3424,7 +3565,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3439,12 +3580,12 @@
         <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" ht="27" spans="1:12">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3462,7 +3603,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3477,15 +3618,15 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
@@ -3500,7 +3641,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3515,12 +3656,12 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" ht="27" spans="1:12">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3538,7 +3679,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3553,12 +3694,12 @@
         <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" ht="40.5" spans="1:12">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3576,7 +3717,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3591,15 +3732,15 @@
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" ht="28.5" spans="1:12">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
@@ -3614,7 +3755,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3629,15 +3770,15 @@
         <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" ht="27" spans="1:12">
       <c r="A22" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
@@ -3652,7 +3793,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3667,12 +3808,12 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" ht="42" spans="1:12">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3690,7 +3831,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3705,15 +3846,15 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
@@ -3728,7 +3869,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3743,12 +3884,12 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" ht="54" spans="1:12">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3766,7 +3907,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3781,15 +3922,15 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" ht="27" spans="1:12">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B26" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
@@ -3804,7 +3945,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3819,12 +3960,12 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" ht="40.5" spans="1:12">
       <c r="A27" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3842,7 +3983,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3854,18 +3995,18 @@
         <v>15</v>
       </c>
       <c r="K27" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L27" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
@@ -3880,7 +4021,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3895,15 +4036,15 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" ht="27" spans="1:12">
       <c r="A29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
@@ -3918,7 +4059,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3933,15 +4074,15 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B30" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
@@ -3956,7 +4097,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3971,12 +4112,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -4009,12 +4150,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" ht="150" spans="1:12">
       <c r="A32" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -4032,7 +4173,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -4047,15 +4188,15 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
@@ -4070,7 +4211,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -4082,15 +4223,15 @@
         <v>15</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" ht="150" spans="1:12">
       <c r="A34" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -4108,7 +4249,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -4123,12 +4264,12 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" ht="69" spans="1:12">
       <c r="A35" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -4146,13 +4287,13 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
       </c>
       <c r="I35" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J35" t="s">
         <v>15</v>
@@ -4161,21 +4302,21 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4184,7 +4325,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4196,15 +4337,15 @@
         <v>15</v>
       </c>
       <c r="K36" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L36" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" ht="40.5" spans="1:12">
       <c r="A37" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -4213,7 +4354,7 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4222,7 +4363,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4234,15 +4375,15 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L37" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" ht="27" spans="1:12">
       <c r="A38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4260,7 +4401,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4275,12 +4416,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" ht="55.5" spans="1:12">
       <c r="A39" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4298,7 +4439,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4313,21 +4454,21 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B40" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C40" t="s">
         <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4336,7 +4477,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4348,15 +4489,15 @@
         <v>15</v>
       </c>
       <c r="K40" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L40" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="41" ht="30" spans="1:12">
       <c r="A41" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4365,7 +4506,7 @@
         <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4374,7 +4515,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4386,18 +4527,18 @@
         <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="L41" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C42" t="s">
         <v>14</v>
@@ -4412,7 +4553,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4427,12 +4568,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" ht="54" spans="1:12">
       <c r="A43" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4450,7 +4591,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4465,21 +4606,21 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B44" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4488,7 +4629,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4500,15 +4641,15 @@
         <v>15</v>
       </c>
       <c r="K44" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L44" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="45" ht="27" spans="1:12">
       <c r="A45" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4517,7 +4658,7 @@
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -4526,7 +4667,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4541,21 +4682,21 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" ht="40.5" spans="1:12">
       <c r="A46" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -4564,7 +4705,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4579,21 +4720,21 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" ht="40.5" spans="1:12">
       <c r="A47" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B47" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -4602,7 +4743,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4614,15 +4755,15 @@
         <v>15</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="L47" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4656,9 +4797,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49" ht="28.5" spans="1:12">
+    <row r="49" ht="45" spans="1:12">
       <c r="A49" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4676,13 +4817,13 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
       </c>
       <c r="I49" t="s">
-        <v>15</v>
+        <v>172</v>
       </c>
       <c r="J49" t="s">
         <v>15</v>
@@ -4691,12 +4832,12 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" ht="54" spans="1:12">
       <c r="A50" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4714,7 +4855,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4729,12 +4870,12 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" ht="43.5" spans="1:12">
       <c r="A51" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4752,7 +4893,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4767,12 +4908,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" ht="69" spans="1:12">
       <c r="A52" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4790,7 +4931,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4805,12 +4946,12 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53" ht="27" spans="1:12">
       <c r="A53" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4828,7 +4969,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4843,12 +4984,12 @@
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="54" ht="27" spans="1:12">
       <c r="A54" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4866,7 +5007,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4881,12 +5022,12 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" ht="40.5" spans="1:12">
       <c r="A55" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4904,7 +5045,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4916,15 +5057,15 @@
         <v>15</v>
       </c>
       <c r="K55" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="L55" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" ht="55.5" spans="1:12">
       <c r="A56" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4942,7 +5083,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4957,15 +5098,15 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B57" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
@@ -4980,7 +5121,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4995,12 +5136,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="58" ht="40.5" spans="1:12">
       <c r="A58" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -5018,7 +5159,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -5033,12 +5174,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="59" ht="28.5" spans="1:12">
       <c r="A59" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -5056,7 +5197,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -5071,15 +5212,15 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="60" ht="28.5" spans="1:12">
       <c r="A60" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B60" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
@@ -5094,7 +5235,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5109,12 +5250,12 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="61" ht="54" spans="1:12">
       <c r="A61" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -5132,7 +5273,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5147,12 +5288,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="62" ht="27" spans="1:12">
       <c r="A62" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -5170,7 +5311,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5185,12 +5326,12 @@
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63" ht="30" spans="1:12">
       <c r="A63" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5208,7 +5349,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5223,12 +5364,12 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="64" ht="55.5" spans="1:12">
       <c r="A64" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5246,7 +5387,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5258,18 +5399,18 @@
         <v>15</v>
       </c>
       <c r="K64" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="L64" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
@@ -5284,7 +5425,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5299,12 +5440,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="66" ht="27" spans="1:12">
       <c r="A66" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5322,7 +5463,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5337,12 +5478,12 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" ht="42" spans="1:12">
       <c r="A67" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5360,7 +5501,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5375,12 +5516,12 @@
         <v>15</v>
       </c>
       <c r="L67" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="68" ht="42" spans="1:12">
       <c r="A68" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5398,7 +5539,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5413,12 +5554,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="69" ht="40.5" spans="1:12">
       <c r="A69" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5436,7 +5577,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5451,12 +5592,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="70" ht="40.5" spans="1:12">
       <c r="A70" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5474,7 +5615,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5489,12 +5630,12 @@
         <v>15</v>
       </c>
       <c r="L70" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" ht="30" spans="1:12">
       <c r="A71" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5518,21 +5659,21 @@
         <v>15</v>
       </c>
       <c r="I71" t="s">
-        <v>15</v>
+        <v>226</v>
       </c>
       <c r="J71" t="s">
         <v>15</v>
       </c>
       <c r="K71" t="s">
-        <v>15</v>
+        <v>227</v>
       </c>
       <c r="L71" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="72" ht="150" spans="1:12">
       <c r="A72" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5550,7 +5691,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5562,18 +5703,18 @@
         <v>15</v>
       </c>
       <c r="K72" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="L72" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B73" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C73" t="s">
         <v>14</v>
@@ -5588,7 +5729,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5603,12 +5744,12 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="74" ht="27" spans="1:12">
       <c r="A74" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5626,7 +5767,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5641,15 +5782,15 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B75" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C75" t="s">
         <v>14</v>
@@ -5664,7 +5805,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5679,15 +5820,15 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="76" ht="28.5" spans="1:12">
       <c r="A76" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B76" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -5702,7 +5843,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5717,12 +5858,12 @@
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="77" ht="54" spans="1:12">
       <c r="A77" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5740,7 +5881,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5755,15 +5896,15 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B78" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
@@ -5778,7 +5919,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5793,12 +5934,12 @@
         <v>15</v>
       </c>
       <c r="L78" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="79" ht="27" spans="1:12">
       <c r="A79" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5816,7 +5957,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5831,12 +5972,12 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="80" ht="28.5" spans="1:12">
       <c r="A80" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5854,7 +5995,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5869,15 +6010,15 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="81" ht="27" spans="1:12">
       <c r="A81" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B81" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C81" t="s">
         <v>14</v>
@@ -5892,7 +6033,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5907,15 +6048,15 @@
         <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B82" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C82" t="s">
         <v>14</v>
@@ -5930,7 +6071,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5945,12 +6086,12 @@
         <v>15</v>
       </c>
       <c r="L82" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="83" ht="42" spans="1:12">
       <c r="A83" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -5968,7 +6109,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5983,15 +6124,15 @@
         <v>15</v>
       </c>
       <c r="L83" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="84" ht="40.5" spans="1:12">
       <c r="A84" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B84" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C84" t="s">
         <v>14</v>
@@ -6006,7 +6147,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -6021,15 +6162,15 @@
         <v>15</v>
       </c>
       <c r="L84" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
     </row>
     <row r="85" ht="27" spans="1:12">
       <c r="A85" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B85" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C85" t="s">
         <v>14</v>
@@ -6044,7 +6185,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6059,12 +6200,12 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="86" ht="54" spans="1:12">
       <c r="A86" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6082,7 +6223,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6097,15 +6238,15 @@
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="87" ht="27" spans="1:12">
       <c r="A87" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B87" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
@@ -6120,7 +6261,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6135,15 +6276,15 @@
         <v>15</v>
       </c>
       <c r="L87" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="88" ht="43.5" spans="1:12">
       <c r="A88" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B88" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
@@ -6158,7 +6299,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6173,12 +6314,12 @@
         <v>15</v>
       </c>
       <c r="L88" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="89" ht="27" spans="1:12">
       <c r="A89" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6196,7 +6337,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6208,15 +6349,15 @@
         <v>15</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="L89" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="90" ht="27" spans="1:12">
       <c r="A90" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -6234,7 +6375,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6249,12 +6390,12 @@
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="91" ht="54" spans="1:12">
       <c r="A91" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6272,7 +6413,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6284,18 +6425,18 @@
         <v>15</v>
       </c>
       <c r="K91" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="L91" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B92" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C92" t="s">
         <v>14</v>
@@ -6310,7 +6451,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6325,12 +6466,12 @@
         <v>15</v>
       </c>
       <c r="L92" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="93" ht="40.5" spans="1:12">
       <c r="A93" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6348,7 +6489,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6363,12 +6504,12 @@
         <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="94" ht="69" spans="1:12">
       <c r="A94" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -6386,7 +6527,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6401,12 +6542,12 @@
         <v>15</v>
       </c>
       <c r="L94" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="95" ht="42" spans="1:12">
       <c r="A95" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6424,7 +6565,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6436,15 +6577,15 @@
         <v>15</v>
       </c>
       <c r="K95" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="L95" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -6482,7 +6623,7 @@
     </row>
     <row r="97" ht="30" spans="1:12">
       <c r="A97" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -6511,8 +6652,8 @@
       <c r="J97" t="s">
         <v>15</v>
       </c>
-      <c r="K97" t="s">
-        <v>300</v>
+      <c r="K97" s="3" t="s">
+        <v>305</v>
       </c>
       <c r="L97" t="s">
         <v>24</v>
@@ -6520,7 +6661,7 @@
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -6550,15 +6691,15 @@
         <v>15</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="L98" t="s">
-        <v>26</v>
+        <v>307</v>
+      </c>
+      <c r="L98" s="4" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -6588,10 +6729,10 @@
         <v>15</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="L99" t="s">
-        <v>26</v>
+        <v>310</v>
+      </c>
+      <c r="L99" s="4" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -6612,39 +6753,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B2" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B3" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
@@ -6652,15 +6793,15 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
@@ -6668,66 +6809,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B10" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B11" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B12" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B13" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B14" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B15" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -6749,616 +6890,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B2" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="C2" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="D2" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="E2" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="F2" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B3" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="C3" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="D3" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="E3" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="F3" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B4" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C4" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="D4" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="E4" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="F4" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B5" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="C5" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="D5" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="E5" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="F5" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B6" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C6" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="D6" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="E6" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="F6" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B7" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="C7" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="D7" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="E7" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="F7" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B8" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C8" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="D8" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="E8" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="F8" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B9" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C9" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="D9" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="E9" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="F9" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B10" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="C10" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="D10" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="E10" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="F10" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B11" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C11" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="D11" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="E11" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="F11" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B12" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="C12" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="D12" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="E12" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="F12" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B13" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="C13" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="D13" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="E13" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="F13" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B14" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="C14" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="D14" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="E14" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="F14" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B15" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="C15" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="D15" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="E15" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="F15" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B16" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C16" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="D16" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="E16" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="F16" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B17" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="C17" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D17" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="E17" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="F17" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B18" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="C18" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="D18" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="E18" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="F18" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B19" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C19" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="D19" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="E19" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="F19" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B20" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C20" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="D20" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="E20" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F20" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B21" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C21" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="D21" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="E21" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="F21" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B22" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="C22" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="D22" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="E22" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="F22" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B23" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="C23" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="D23" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="E23" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="F23" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B24" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="C24" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="D24" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="E24" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="F24" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B25" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C25" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="D25" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="E25" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F25" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B26" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="C26" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="D26" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="E26" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="F26" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B27" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="C27" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="D27" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="E27" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="F27" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B28" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="C28" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="D28" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="E28" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="F28" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B29" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="C29" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="D29" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="E29" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="F29" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B30" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="C30" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="D30" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="E30" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="F30" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="B31" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="C31" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="D31" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
   </sheetData>
